--- a/data/trans_orig/IP2002-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2002-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15193</t>
+          <t>15545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39277</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46267</t>
+          <t>46222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44076</t>
+          <t>44438</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51808</t>
+          <t>51810</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87070</t>
+          <t>86718</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96587</t>
+          <t>96648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>14917</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14916</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12207</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25113</t>
+          <t>25772</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80042</t>
+          <t>79901</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89229</t>
+          <t>89162</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90599</t>
+          <t>91215</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100295</t>
+          <t>100909</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>175220</t>
+          <t>174561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188126</t>
+          <t>187482</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56943</t>
+          <t>57130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63250</t>
+          <t>63215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62456</t>
+          <t>62807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121913</t>
+          <t>121396</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128595</t>
+          <t>128986</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61651</t>
+          <t>61719</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68557</t>
+          <t>68771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72582</t>
+          <t>72939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137998</t>
+          <t>137222</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>145248</t>
+          <t>145014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4884</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32336</t>
+          <t>32962</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38582</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32524</t>
+          <t>33233</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40565</t>
+          <t>40590</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68616</t>
+          <t>67737</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77759</t>
+          <t>77807</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12140</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48606</t>
+          <t>47968</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52760</t>
+          <t>52761</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47434</t>
+          <t>47657</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54576</t>
+          <t>54902</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98366</t>
+          <t>98072</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>106729</t>
+          <t>106594</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14238</t>
+          <t>15304</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113080</t>
+          <t>113663</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121020</t>
+          <t>121062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>112158</t>
+          <t>111092</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>121659</t>
+          <t>121652</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>229429</t>
+          <t>228483</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>241086</t>
+          <t>240773</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20586</t>
+          <t>20101</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>22248</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20204</t>
+          <t>20657</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37689</t>
+          <t>37701</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>130289</t>
+          <t>130774</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>142442</t>
+          <t>142330</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>133172</t>
+          <t>133246</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>145666</t>
+          <t>145332</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>268680</t>
+          <t>268668</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>286165</t>
+          <t>285712</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>36410</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>57038</t>
+          <t>58466</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40380</t>
+          <t>40242</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61774</t>
+          <t>62884</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>80403</t>
+          <t>81343</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>111998</t>
+          <t>110831</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>588002</t>
+          <t>586574</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>609418</t>
+          <t>608630</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>623249</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>644643</t>
+          <t>644781</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1218065</t>
+          <t>1219232</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1249660</t>
+          <t>1248720</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>15346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>20360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46155</t>
+          <t>46567</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52975</t>
+          <t>53161</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45200</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55018</t>
+          <t>54907</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95167</t>
+          <t>94855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106783</t>
+          <t>106679</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15469</t>
+          <t>16098</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87810</t>
+          <t>87825</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94622</t>
+          <t>94636</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89644</t>
+          <t>88981</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>98166</t>
+          <t>98048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>181155</t>
+          <t>180526</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>191427</t>
+          <t>191579</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56227</t>
+          <t>56230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62122</t>
+          <t>62121</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60102</t>
+          <t>59621</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65723</t>
+          <t>65693</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118556</t>
+          <t>119097</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126516</t>
+          <t>126760</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10391</t>
+          <t>10483</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63164</t>
+          <t>63072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70896</t>
+          <t>70714</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71009</t>
+          <t>71481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78180</t>
+          <t>78202</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138058</t>
+          <t>137506</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147665</t>
+          <t>147789</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33040</t>
+          <t>33026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39767</t>
+          <t>40410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35371</t>
+          <t>36348</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>43225</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72610</t>
+          <t>71634</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>81916</t>
+          <t>81576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7094</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>16089</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41480</t>
+          <t>41979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48327</t>
+          <t>48338</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43304</t>
+          <t>43016</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51695</t>
+          <t>51344</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>88092</t>
+          <t>87870</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98289</t>
+          <t>98325</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>11835</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>12598</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8567</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22102</t>
+          <t>21689</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115686</t>
+          <t>115705</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124560</t>
+          <t>124509</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>117890</t>
+          <t>117977</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>127283</t>
+          <t>127383</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>236013</t>
+          <t>236426</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>249548</t>
+          <t>249341</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11151</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>13391</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21738</t>
+          <t>21007</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>146497</t>
+          <t>146908</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154525</t>
+          <t>154491</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>151794</t>
+          <t>151291</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>160272</t>
+          <t>160146</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>300592</t>
+          <t>301323</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>313202</t>
+          <t>313313</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27367</t>
+          <t>28359</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47763</t>
+          <t>47592</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38044</t>
+          <t>38542</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60920</t>
+          <t>60200</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71459</t>
+          <t>71872</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>101364</t>
+          <t>103048</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>615128</t>
+          <t>615299</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>635524</t>
+          <t>634532</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>641779</t>
+          <t>642499</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>664655</t>
+          <t>664157</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1264227</t>
+          <t>1262543</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1294132</t>
+          <t>1293719</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44762</t>
+          <t>44381</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52111</t>
+          <t>52461</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52556</t>
+          <t>52286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>59749</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100477</t>
+          <t>100071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110340</t>
+          <t>110137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91769</t>
+          <t>92188</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93835</t>
+          <t>94157</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103351</t>
+          <t>103260</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189331</t>
+          <t>189456</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200349</t>
+          <t>200190</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56279</t>
+          <t>56400</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63070</t>
+          <t>62191</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122306</t>
+          <t>121885</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16287</t>
+          <t>16537</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13939</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12279</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26186</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56475</t>
+          <t>56225</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66785</t>
+          <t>66554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63823</t>
+          <t>64641</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73806</t>
+          <t>73758</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124338</t>
+          <t>125147</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138245</t>
+          <t>138785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37768</t>
+          <t>37155</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37436</t>
+          <t>37525</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>77725</t>
+          <t>77703</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82921</t>
+          <t>82920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>778</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15999</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39455</t>
+          <t>39030</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47889</t>
+          <t>47596</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46296</t>
+          <t>46783</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53122</t>
+          <t>53147</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89055</t>
+          <t>89037</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>99362</t>
+          <t>99698</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119493</t>
+          <t>119470</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>127263</t>
+          <t>127331</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127565</t>
+          <t>127055</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>133147</t>
+          <t>133140</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>250530</t>
+          <t>250603</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>259376</t>
+          <t>259528</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>12130</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22015</t>
+          <t>22333</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>135064</t>
+          <t>135147</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>144572</t>
+          <t>144671</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>146302</t>
+          <t>146672</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155375</t>
+          <t>155362</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>285712</t>
+          <t>285394</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>298499</t>
+          <t>297789</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>31165</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52486</t>
+          <t>52117</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45040</t>
+          <t>44593</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>61774</t>
+          <t>61321</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>90001</t>
+          <t>89220</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>606345</t>
+          <t>606714</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>627430</t>
+          <t>627666</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>655855</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>674742</t>
+          <t>675609</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1269725</t>
+          <t>1270506</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1297952</t>
+          <t>1298405</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13581</t>
+          <t>12508</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20603</t>
+          <t>20325</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59280</t>
+          <t>60353</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70689</t>
+          <t>70680</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64357</t>
+          <t>64536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74424</t>
+          <t>74288</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129266</t>
+          <t>129544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143096</t>
+          <t>143561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11620</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>13441</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19817</t>
+          <t>19371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113991</t>
+          <t>113467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123698</t>
+          <t>124043</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111985</t>
+          <t>111227</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>122512</t>
+          <t>122398</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>230462</t>
+          <t>230908</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>244667</t>
+          <t>244661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18173</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45422</t>
+          <t>45503</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53366</t>
+          <t>53283</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55797</t>
+          <t>55696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63139</t>
+          <t>63384</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104182</t>
+          <t>103888</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114826</t>
+          <t>115145</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63930</t>
+          <t>63880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72836</t>
+          <t>72472</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138621</t>
+          <t>138972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>10856</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27388</t>
+          <t>27158</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32653</t>
+          <t>32665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34546</t>
+          <t>34777</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39630</t>
+          <t>39696</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64538</t>
+          <t>64063</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71498</t>
+          <t>71331</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>360</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8636</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38313</t>
+          <t>38320</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43280</t>
+          <t>43293</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49071</t>
+          <t>48792</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53811</t>
+          <t>53800</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89436</t>
+          <t>90026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96683</t>
+          <t>96685</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>18397</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21388</t>
+          <t>21737</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>17367</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34796</t>
+          <t>35521</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>104937</t>
+          <t>105182</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>116274</t>
+          <t>117044</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>133469</t>
+          <t>133120</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>147213</t>
+          <t>147933</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>243639</t>
+          <t>242914</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>261787</t>
+          <t>261068</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>122058</t>
+          <t>123445</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129108</t>
+          <t>129139</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>147936</t>
+          <t>148416</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>154415</t>
+          <t>154410</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>274273</t>
+          <t>275058</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>282822</t>
+          <t>282863</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>28474</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51005</t>
+          <t>50197</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27882</t>
+          <t>27386</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50173</t>
+          <t>49894</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62221</t>
+          <t>61602</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93246</t>
+          <t>92702</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>605066</t>
+          <t>605874</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>626842</t>
+          <t>627597</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>697292</t>
+          <t>697571</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>719583</t>
+          <t>720079</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1310290</t>
+          <t>1310834</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1341315</t>
+          <t>1341934</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
